--- a/ig/main/CodeSystem-terminologie-SERAFINPH.xlsx
+++ b/ig/main/CodeSystem-terminologie-SERAFINPH.xlsx
@@ -80,7 +80,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>ANS (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ig/main/CodeSystem-terminologie-SERAFINPH.xlsx
+++ b/ig/main/CodeSystem-terminologie-SERAFINPH.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>2023.1.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/main/CodeSystem-terminologie-SERAFINPH.xlsx
+++ b/ig/main/CodeSystem-terminologie-SERAFINPH.xlsx
@@ -86,7 +86,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
